--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574674996</v>
+        <v>46157.93118540286</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118540286</v>
+        <v>46157.9318397147</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318397147</v>
+        <v>46157.93405971022</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405971022</v>
+        <v>46157.93724053094</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724053094</v>
+        <v>46158.28221850112</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221850112</v>
+        <v>46158.29702750034</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29702750034</v>
+        <v>46158.29821640162</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821640162</v>
+        <v>46158.33392816146</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392816146</v>
+        <v>46158.36862604078</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862604078</v>
+        <v>46158.37293569906</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
